--- a/Configs/GameConfig/Datas/fg/#ResearchNode-研发节点.xlsx
+++ b/Configs/GameConfig/Datas/fg/#ResearchNode-研发节点.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P69"/>
+  <dimension ref="A1:P71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3816,31 +3816,31 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>environment.purifier_t2</t>
+          <t>signal.listening_post</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>environment</t>
+          <t>signal</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>research.node.environment.purifier_t2</t>
+          <t>research.node.signal.listening_post</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>research.node.environment.purifier_t2.desc</t>
+          <t>research.node.signal.listening_post.desc</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>upgrade</t>
+          <t>building</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -3849,12 +3849,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>listening_array_core:1</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>build:listening_post</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3874,11 +3874,11 @@
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>FG7-ENV-04</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -3886,22 +3886,22 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>environment.purifier_t3</t>
+          <t>signal.listening_t2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>environment</t>
+          <t>signal</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>research.node.environment.purifier_t3</t>
+          <t>research.node.signal.listening_t2</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>research.node.environment.purifier_t3.desc</t>
+          <t>research.node.signal.listening_t2.desc</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3910,11 +3910,11 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>environment.purifier_t2</t>
+          <t>signal.listening_post</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3944,11 +3944,11 @@
         <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>FG7-ENV-04</t>
+          <t>FG7-ENV-03</t>
         </is>
       </c>
     </row>
@@ -3956,7 +3956,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>environment.roof</t>
+          <t>environment.purifier_t2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3966,21 +3966,21 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>research.node.environment.roof</t>
+          <t>research.node.environment.purifier_t2</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>research.node.environment.roof.desc</t>
+          <t>research.node.environment.purifier_t2.desc</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>upgrade</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -4014,11 +4014,11 @@
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>FG7-ENV-03</t>
+          <t>FG7-ENV-04</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>environment.damper</t>
+          <t>environment.purifier_t3</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4036,25 +4036,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>research.node.environment.damper</t>
+          <t>research.node.environment.purifier_t3</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>research.node.environment.damper.desc</t>
+          <t>research.node.environment.purifier_t3.desc</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>upgrade</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>environment.purifier_t2</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4081,14 +4081,14 @@
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>FG12-EVT-02</t>
+          <t>FG7-ENV-04</t>
         </is>
       </c>
     </row>
@@ -4096,27 +4096,27 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>expedition.cargo_1</t>
+          <t>environment.roof</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>expedition</t>
+          <t>environment</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>research.node.expedition.cargo_1</t>
+          <t>research.node.environment.roof</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>research.node.expedition.cargo_1.desc</t>
+          <t>research.node.environment.roof.desc</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>capacity</t>
+          <t>building</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -4154,11 +4154,11 @@
         <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>FG8-LOOT-03</t>
+          <t>FG7-ENV-03</t>
         </is>
       </c>
     </row>
@@ -4166,35 +4166,35 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>expedition.cargo_2</t>
+          <t>environment.damper</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>expedition</t>
+          <t>environment</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>research.node.expedition.cargo_2</t>
+          <t>research.node.environment.damper</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>research.node.expedition.cargo_2.desc</t>
+          <t>research.node.environment.damper.desc</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>capacity</t>
+          <t>building</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>expedition.cargo_1</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -4221,14 +4221,14 @@
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>FG8-LOOT-03</t>
+          <t>FG12-EVT-02</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>expedition.squad_plus</t>
+          <t>expedition.cargo_1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4246,12 +4246,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>research.node.expedition.squad_plus</t>
+          <t>research.node.expedition.cargo_1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>research.node.expedition.squad_plus.desc</t>
+          <t>research.node.expedition.cargo_1.desc</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4260,7 +4260,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -4294,11 +4294,11 @@
         <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>FG8-EXP-01</t>
+          <t>FG8-LOOT-03</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>expedition.march_speed</t>
+          <t>expedition.cargo_2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4316,25 +4316,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>research.node.expedition.march_speed</t>
+          <t>research.node.expedition.cargo_2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>research.node.expedition.march_speed.desc</t>
+          <t>research.node.expedition.cargo_2.desc</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>efficiency</t>
+          <t>capacity</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>expedition.cargo_1</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4361,14 +4361,14 @@
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>FG8-EXP-02</t>
+          <t>FG8-LOOT-03</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>expedition.drop_t2</t>
+          <t>expedition.squad_plus</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4386,21 +4386,21 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>research.node.expedition.drop_t2</t>
+          <t>research.node.expedition.squad_plus</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>research.node.expedition.drop_t2.desc</t>
+          <t>research.node.expedition.squad_plus.desc</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>upgrade</t>
+          <t>capacity</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -4431,14 +4431,14 @@
         <v>0</v>
       </c>
       <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
         <v>1</v>
       </c>
-      <c r="O57" t="n">
-        <v>3</v>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>FG8-DROP-01</t>
+          <t>FG8-EXP-01</t>
         </is>
       </c>
     </row>
@@ -4446,31 +4446,31 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>silent.component</t>
+          <t>expedition.march_speed</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>silent</t>
+          <t>expedition</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>research.node.silent.component</t>
+          <t>research.node.expedition.march_speed</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>research.node.silent.component.desc</t>
+          <t>research.node.expedition.march_speed.desc</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>blueprint</t>
+          <t>efficiency</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -4504,11 +4504,11 @@
         <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>FG9-FAC-01</t>
+          <t>FG8-EXP-02</t>
         </is>
       </c>
     </row>
@@ -4516,35 +4516,35 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>silent.module</t>
+          <t>expedition.drop_t2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>silent</t>
+          <t>expedition</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>research.node.silent.module</t>
+          <t>research.node.expedition.drop_t2</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>research.node.silent.module.desc</t>
+          <t>research.node.expedition.drop_t2.desc</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>blueprint</t>
+          <t>upgrade</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>silent.component</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4574,11 +4574,11 @@
         <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>FG9-FAC-01</t>
+          <t>FG8-DROP-01</t>
         </is>
       </c>
     </row>
@@ -4586,7 +4586,7 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>silent.turret</t>
+          <t>silent.component</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>research.node.silent.turret</t>
+          <t>research.node.silent.component</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>research.node.silent.turret.desc</t>
+          <t>research.node.silent.component.desc</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4610,11 +4610,11 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>silent.module</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4641,7 +4641,7 @@
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -4656,22 +4656,22 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>foundry.component</t>
+          <t>silent.module</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>foundry</t>
+          <t>silent</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>research.node.foundry.component</t>
+          <t>research.node.silent.module</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>research.node.foundry.component.desc</t>
+          <t>research.node.silent.module.desc</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4680,11 +4680,11 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>silent.component</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4711,14 +4711,14 @@
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>FG9-FAC-02</t>
+          <t>FG9-FAC-01</t>
         </is>
       </c>
     </row>
@@ -4726,22 +4726,22 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>foundry.module</t>
+          <t>silent.turret</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>foundry</t>
+          <t>silent</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>research.node.foundry.module</t>
+          <t>research.node.silent.turret</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>research.node.foundry.module.desc</t>
+          <t>research.node.silent.turret.desc</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4750,11 +4750,11 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>foundry.component</t>
+          <t>silent.module</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4781,14 +4781,14 @@
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>FG9-FAC-02</t>
+          <t>FG9-FAC-01</t>
         </is>
       </c>
     </row>
@@ -4796,7 +4796,7 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>foundry.turret</t>
+          <t>foundry.component</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4806,12 +4806,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>research.node.foundry.turret</t>
+          <t>research.node.foundry.component</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>research.node.foundry.turret.desc</t>
+          <t>research.node.foundry.component.desc</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4820,11 +4820,11 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>foundry.module</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4851,7 +4851,7 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -4866,22 +4866,22 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>clarity.component</t>
+          <t>foundry.module</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>clarity</t>
+          <t>foundry</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>research.node.clarity.component</t>
+          <t>research.node.foundry.module</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>research.node.clarity.component.desc</t>
+          <t>research.node.foundry.module.desc</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4890,11 +4890,11 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>foundry.component</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4921,14 +4921,14 @@
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>FG10-FAC-01</t>
+          <t>FG9-FAC-02</t>
         </is>
       </c>
     </row>
@@ -4936,22 +4936,22 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>clarity.module</t>
+          <t>foundry.turret</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>clarity</t>
+          <t>foundry</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>research.node.clarity.module</t>
+          <t>research.node.foundry.turret</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>research.node.clarity.module.desc</t>
+          <t>research.node.foundry.turret.desc</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4960,11 +4960,11 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>clarity.component</t>
+          <t>foundry.module</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4991,14 +4991,14 @@
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>FG10-FAC-01</t>
+          <t>FG9-FAC-02</t>
         </is>
       </c>
     </row>
@@ -5006,7 +5006,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>clarity.turret</t>
+          <t>clarity.component</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>research.node.clarity.turret</t>
+          <t>research.node.clarity.component</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>research.node.clarity.turret.desc</t>
+          <t>research.node.clarity.component.desc</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5030,11 +5030,11 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>clarity.module</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -5061,7 +5061,7 @@
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -5076,22 +5076,22 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>overclock.component</t>
+          <t>clarity.module</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>overclock</t>
+          <t>clarity</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>research.node.overclock.component</t>
+          <t>research.node.clarity.module</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>research.node.overclock.component.desc</t>
+          <t>research.node.clarity.module.desc</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5100,11 +5100,11 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>clarity.component</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5131,14 +5131,14 @@
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>FG11-FAC-01</t>
+          <t>FG10-FAC-01</t>
         </is>
       </c>
     </row>
@@ -5146,22 +5146,22 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>overclock.module</t>
+          <t>clarity.turret</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>overclock</t>
+          <t>clarity</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>research.node.overclock.module</t>
+          <t>research.node.clarity.turret</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>research.node.overclock.module.desc</t>
+          <t>research.node.clarity.turret.desc</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5170,11 +5170,11 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>overclock.component</t>
+          <t>clarity.module</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -5201,14 +5201,14 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>FG11-FAC-01</t>
+          <t>FG10-FAC-01</t>
         </is>
       </c>
     </row>
@@ -5216,67 +5216,207 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
+          <t>overclock.component</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>overclock</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>research.node.overclock.component</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>research.node.overclock.component.desc</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>blueprint</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>20</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>FG11-FAC-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>overclock.module</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>overclock</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>research.node.overclock.module</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>research.node.overclock.module.desc</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>blueprint</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>30</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>overclock.component</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>1</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>FG11-FAC-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
           <t>overclock.turret</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>overclock</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>research.node.overclock.turret</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>research.node.overclock.turret.desc</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>blueprint</t>
         </is>
       </c>
-      <c r="G69" t="n">
+      <c r="G71" t="n">
         <v>45</v>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>overclock.module</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="M69" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" t="n">
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
         <v>2</v>
       </c>
-      <c r="O69" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" t="inlineStr">
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="inlineStr">
         <is>
           <t>FG11-FAC-01</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#ResearchNode-研发节点.xlsx
+++ b/Configs/GameConfig/Datas/fg/#ResearchNode-研发节点.xlsx
@@ -2996,7 +2996,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>upgrade</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>tier:turret_light.t2,tier:turret_heavy.t2</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>FG6-DEF-01</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>upgrade</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>tier:turret_light.t3,tier:turret_heavy.t3</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>FG6-DEF-01</t>
+          <t>none</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/fg/#ResearchNode-研发节点.xlsx
+++ b/Configs/GameConfig/Datas/fg/#ResearchNode-研发节点.xlsx
@@ -3154,7 +3154,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>build:barrier_t1,build:barrier_t2,build:barrier_t3,build:gate</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>FG6-DEF-02</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>build:shield_gen</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>FG6-DEF-02</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>build:trap_emitter</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>FG6-DEF-02</t>
+          <t>none</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/fg/#ResearchNode-研发节点.xlsx
+++ b/Configs/GameConfig/Datas/fg/#ResearchNode-研发节点.xlsx
@@ -3364,7 +3364,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>build:repair_drone_station</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>FG6-DEF-03</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>rule:auto_rebuild</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>FG6-DEF-03</t>
+          <t>none</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/fg/#ResearchNode-研发节点.xlsx
+++ b/Configs/GameConfig/Datas/fg/#ResearchNode-研发节点.xlsx
@@ -2244,7 +2244,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>build:pipe_t3</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>FG7-ENV-03</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>tier:listening_post.t2</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>FG7-ENV-03</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>build:roof</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>FG7-ENV-03</t>
+          <t>none</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/fg/#ResearchNode-研发节点.xlsx
+++ b/Configs/GameConfig/Datas/fg/#ResearchNode-研发节点.xlsx
@@ -3994,7 +3994,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>tier:purifier.t2</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>FG7-ENV-04</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -4059,12 +4059,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>reactor_core:1</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>tier:purifier.t3</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>FG7-ENV-04</t>
+          <t>none</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/fg/#ResearchNode-研发节点.xlsx
+++ b/Configs/GameConfig/Datas/fg/#ResearchNode-研发节点.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P71"/>
+  <dimension ref="A1:P72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4516,7 +4516,7 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>expedition.drop_t2</t>
+          <t>expedition.drop_station</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4526,21 +4526,21 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>research.node.expedition.drop_t2</t>
+          <t>research.node.expedition.drop_station</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>research.node.expedition.drop_t2.desc</t>
+          <t>research.node.expedition.drop_station.desc</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>upgrade</t>
+          <t>building</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>build:drop_station</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4571,14 +4571,14 @@
         <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>3</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>FG8-DROP-01</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -4586,27 +4586,27 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>silent.component</t>
+          <t>expedition.drop_t2</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>silent</t>
+          <t>expedition</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>research.node.silent.component</t>
+          <t>research.node.expedition.drop_t2</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>research.node.silent.component.desc</t>
+          <t>research.node.expedition.drop_t2.desc</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>blueprint</t>
+          <t>upgrade</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>expedition.drop_station</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>tier:drop_station.t2</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4641,14 +4641,14 @@
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>FG9-FAC-01</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -4656,7 +4656,7 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>silent.module</t>
+          <t>silent.component</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>research.node.silent.module</t>
+          <t>research.node.silent.component</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>research.node.silent.module.desc</t>
+          <t>research.node.silent.component.desc</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4680,11 +4680,11 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>silent.component</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4711,7 +4711,7 @@
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -4726,7 +4726,7 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>silent.turret</t>
+          <t>silent.module</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4736,12 +4736,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>research.node.silent.turret</t>
+          <t>research.node.silent.module</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>research.node.silent.turret.desc</t>
+          <t>research.node.silent.module.desc</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4750,11 +4750,11 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>silent.module</t>
+          <t>silent.component</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4781,7 +4781,7 @@
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -4796,22 +4796,22 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>foundry.component</t>
+          <t>silent.turret</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>foundry</t>
+          <t>silent</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>research.node.foundry.component</t>
+          <t>research.node.silent.turret</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>research.node.foundry.component.desc</t>
+          <t>research.node.silent.turret.desc</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4820,11 +4820,11 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>silent.module</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4851,14 +4851,14 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>FG9-FAC-02</t>
+          <t>FG9-FAC-01</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>foundry.module</t>
+          <t>foundry.component</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>research.node.foundry.module</t>
+          <t>research.node.foundry.component</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>research.node.foundry.module.desc</t>
+          <t>research.node.foundry.component.desc</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4890,11 +4890,11 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>foundry.component</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4921,7 +4921,7 @@
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -4936,7 +4936,7 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>foundry.turret</t>
+          <t>foundry.module</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>research.node.foundry.turret</t>
+          <t>research.node.foundry.module</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>research.node.foundry.turret.desc</t>
+          <t>research.node.foundry.module.desc</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4960,11 +4960,11 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>foundry.module</t>
+          <t>foundry.component</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4991,7 +4991,7 @@
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -5006,22 +5006,22 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>clarity.component</t>
+          <t>foundry.turret</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>clarity</t>
+          <t>foundry</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>research.node.clarity.component</t>
+          <t>research.node.foundry.turret</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>research.node.clarity.component.desc</t>
+          <t>research.node.foundry.turret.desc</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5030,11 +5030,11 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>foundry.module</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -5061,14 +5061,14 @@
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>FG10-FAC-01</t>
+          <t>FG9-FAC-02</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>clarity.module</t>
+          <t>clarity.component</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>research.node.clarity.module</t>
+          <t>research.node.clarity.component</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>research.node.clarity.module.desc</t>
+          <t>research.node.clarity.component.desc</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5100,11 +5100,11 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>clarity.component</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5131,7 +5131,7 @@
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -5146,7 +5146,7 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>clarity.turret</t>
+          <t>clarity.module</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>research.node.clarity.turret</t>
+          <t>research.node.clarity.module</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>research.node.clarity.turret.desc</t>
+          <t>research.node.clarity.module.desc</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5170,11 +5170,11 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>clarity.module</t>
+          <t>clarity.component</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -5201,7 +5201,7 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -5216,22 +5216,22 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>overclock.component</t>
+          <t>clarity.turret</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>overclock</t>
+          <t>clarity</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>research.node.overclock.component</t>
+          <t>research.node.clarity.turret</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>research.node.overclock.component.desc</t>
+          <t>research.node.clarity.turret.desc</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5240,11 +5240,11 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>clarity.module</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -5271,14 +5271,14 @@
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>FG11-FAC-01</t>
+          <t>FG10-FAC-01</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>overclock.module</t>
+          <t>overclock.component</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>research.node.overclock.module</t>
+          <t>research.node.overclock.component</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>research.node.overclock.module.desc</t>
+          <t>research.node.overclock.component.desc</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5310,11 +5310,11 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>overclock.component</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -5341,7 +5341,7 @@
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -5356,67 +5356,137 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
+          <t>overclock.module</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>overclock</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>research.node.overclock.module</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>research.node.overclock.module.desc</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>blueprint</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>30</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>overclock.component</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>1</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>FG11-FAC-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
           <t>overclock.turret</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>overclock</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>research.node.overclock.turret</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>research.node.overclock.turret.desc</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>blueprint</t>
         </is>
       </c>
-      <c r="G71" t="n">
+      <c r="G72" t="n">
         <v>45</v>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>overclock.module</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" t="n">
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
         <v>2</v>
       </c>
-      <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" t="inlineStr">
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="inlineStr">
         <is>
           <t>FG11-FAC-01</t>
         </is>
